--- a/reports/pdf_rolling5_20260706.xlsx
+++ b/reports/pdf_rolling5_20260706.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -563,14 +563,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-06-29 ~ 2026-07-06  (최근 5거래일)  ·  캡처 4/7  ·  대기: TIME, TIME, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-06-29 ~ 2026-07-06  (최근 5거래일)  ·  캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,341억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 14종목  /  매도 10종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,385억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 14종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -666,10 +666,10 @@
         <v>52</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>563857840</v>
+        <v>562794960</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.106</v>
+        <v>0.105</v>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -685,10 +685,10 @@
         <v>-70</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-997446100</v>
+        <v>-995565900</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>-0.187</v>
+        <v>-0.185</v>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
@@ -706,10 +706,10 @@
         <v>45</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2053035000</v>
+        <v>2049165000</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.384</v>
+        <v>0.381</v>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -725,10 +725,10 @@
         <v>-57</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-5019591000</v>
+        <v>-5010129000</v>
       </c>
       <c r="J7" s="16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.93</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -746,10 +746,10 @@
         <v>33</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1437283650</v>
+        <v>1434574350</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.269</v>
+        <v>0.266</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -765,10 +765,10 @@
         <v>-49</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-2739820300</v>
+        <v>-2734655700</v>
       </c>
       <c r="J8" s="16" t="n">
-        <v>-0.513</v>
+        <v>-0.508</v>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>526584910</v>
+        <v>525592290</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
         <v>-46</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-5246645000</v>
+        <v>-5236755000</v>
       </c>
       <c r="J9" s="16" t="n">
-        <v>-0.982</v>
+        <v>-0.973</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         <v>22</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2135793000</v>
+        <v>2131767000</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.4</v>
+        <v>0.396</v>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
@@ -845,10 +845,10 @@
         <v>-36</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-504187200</v>
+        <v>-503236800</v>
       </c>
       <c r="J10" s="16" t="n">
-        <v>-0.094</v>
+        <v>-0.093</v>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
@@ -866,10 +866,10 @@
         <v>15</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2118286500</v>
+        <v>2114293500</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>0.397</v>
+        <v>0.393</v>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
@@ -885,10 +885,10 @@
         <v>-33</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-4681238100</v>
+        <v>-4672413900</v>
       </c>
       <c r="J11" s="16" t="n">
-        <v>-0.876</v>
+        <v>-0.868</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -906,10 +906,10 @@
         <v>14</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1938447000</v>
+        <v>1934793000</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -925,10 +925,10 @@
         <v>-24</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-2223007200</v>
+        <v>-2218816800</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>-0.416</v>
+        <v>-0.412</v>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
@@ -946,10 +946,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>549120550</v>
+        <v>548085450</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
@@ -965,10 +965,10 @@
         <v>-19</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-1701419600</v>
+        <v>-1698212400</v>
       </c>
       <c r="J13" s="16" t="n">
-        <v>-0.319</v>
+        <v>-0.315</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
         <v>10</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1526779000</v>
+        <v>1523901000</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.286</v>
+        <v>0.283</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
@@ -1005,10 +1005,10 @@
         <v>-6</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-3087510000</v>
+        <v>-3081690000</v>
       </c>
       <c r="J14" s="16" t="n">
-        <v>-0.578</v>
+        <v>-0.572</v>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
@@ -1019,21 +1019,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>473630400</v>
+        <v>2166714000</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.089</v>
+        <v>0.402</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>33→39</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1045,10 +1045,10 @@
         <v>-3</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-798933000</v>
+        <v>-797427000</v>
       </c>
       <c r="J15" s="16" t="n">
-        <v>-0.15</v>
+        <v>-0.148</v>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
@@ -1059,21 +1059,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2170806000</v>
+        <v>472737600</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.406</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>33→39</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1092,10 +1092,10 @@
         <v>5</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>433418500</v>
+        <v>432601500</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.081</v>
+        <v>0.08</v>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
@@ -1118,10 +1118,10 @@
         <v>4</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1449326000</v>
+        <v>1446594000</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.271</v>
+        <v>0.269</v>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
@@ -1144,10 +1144,10 @@
         <v>3</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>724132500</v>
+        <v>722767500</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.136</v>
+        <v>0.134</v>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
     <row r="21" ht="19" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,858억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 2종목  /  매도 1종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,769억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 2종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B21" s="4" t="n"/>
@@ -1259,10 +1259,10 @@
         <v>68</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>455137600</v>
+        <v>460659200</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.094</v>
+        <v>0.097</v>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
@@ -1278,10 +1278,10 @@
         <v>-20</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1722922000</v>
+        <v>-1743824000</v>
       </c>
       <c r="J24" s="16" t="n">
-        <v>-0.355</v>
+        <v>-0.366</v>
       </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
@@ -1299,10 +1299,10 @@
         <v>6</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>1597713000</v>
+        <v>1617096000</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.329</v>
+        <v>0.339</v>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
@@ -1316,1143 +1316,1357 @@
       <c r="K25" s="17" t="n"/>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="n"/>
-      <c r="C27" s="19" t="n"/>
-      <c r="D27" s="19" t="n"/>
-      <c r="E27" s="19" t="n"/>
-      <c r="F27" s="19" t="n"/>
-      <c r="G27" s="19" t="n"/>
-      <c r="H27" s="19" t="n"/>
-      <c r="I27" s="19" t="n"/>
-      <c r="J27" s="19" t="n"/>
-      <c r="K27" s="19" t="n"/>
-    </row>
-    <row r="29" ht="19" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="n"/>
-      <c r="C29" s="19" t="n"/>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="19" t="n"/>
-      <c r="F29" s="19" t="n"/>
-      <c r="G29" s="19" t="n"/>
-      <c r="H29" s="19" t="n"/>
-      <c r="I29" s="19" t="n"/>
-      <c r="J29" s="19" t="n"/>
-      <c r="K29" s="19" t="n"/>
-    </row>
-    <row r="31" ht="19" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 355억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 16종목  /  매도 14종목</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 3,420억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 1종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="8" t="n"/>
+      <c r="J28" s="8" t="n"/>
+      <c r="K28" s="8" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K29" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>2417316300</v>
+      </c>
+      <c r="D30" s="12" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>19→40</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>-39</v>
+      </c>
+      <c r="I30" s="15" t="n">
+        <v>-2751313500</v>
+      </c>
+      <c r="J30" s="16" t="n">
+        <v>-0.804</v>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>189→150</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="19" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,814억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 0종목  /  매도 1종목</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="8" t="n"/>
+      <c r="J33" s="8" t="n"/>
+      <c r="K33" s="8" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>전체대비비중</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="G34" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="H34" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J33" s="9" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>전체대비비중</t>
         </is>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="K34" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
-        <is>
-          <t>더블유씨피</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="C34" s="11" t="n">
-        <v>63808000</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>2,940→3,020</t>
-        </is>
-      </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>LS증권</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
-        <v>-167</v>
-      </c>
-      <c r="I34" s="15" t="n">
-        <v>-88844000</v>
-      </c>
-      <c r="J34" s="16" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>452→285</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="10" t="inlineStr">
-        <is>
-          <t>오로스테크놀로지</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>42012000</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>58→85</t>
-        </is>
-      </c>
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>-111</v>
+        <v>-5</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-216672000</v>
+        <v>-366282000</v>
       </c>
       <c r="J35" s="16" t="n">
-        <v>-0.61</v>
+        <v>-0.13</v>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>647→536</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t>원익IPS</t>
-        </is>
-      </c>
-      <c r="B36" s="11" t="n">
-        <v>25</v>
-      </c>
-      <c r="C36" s="11" t="n">
-        <v>263200000</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>0.741</v>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>60→85</t>
-        </is>
-      </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>씨어스</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>-110</v>
-      </c>
-      <c r="I36" s="15" t="n">
-        <v>-336160000</v>
-      </c>
-      <c r="J36" s="16" t="n">
-        <v>-0.946</v>
-      </c>
-      <c r="K36" s="13" t="inlineStr">
-        <is>
-          <t>843→733</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>동진쎄미켐</t>
-        </is>
-      </c>
-      <c r="B37" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="C37" s="11" t="n">
-        <v>93288000</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>134→157</t>
-        </is>
-      </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>다우데이타</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>-32</v>
-      </c>
-      <c r="I37" s="15" t="n">
-        <v>-45209600</v>
-      </c>
-      <c r="J37" s="16" t="n">
-        <v>-0.127</v>
-      </c>
-      <c r="K37" s="13" t="inlineStr">
-        <is>
-          <t>107→75</t>
-        </is>
-      </c>
+          <t>500→495</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 366억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 16종목  /  매도 14종목</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="inlineStr">
-        <is>
-          <t>네패스아크  (신규)</t>
-        </is>
-      </c>
-      <c r="B38" s="11" t="n">
-        <v>21</v>
-      </c>
-      <c r="C38" s="11" t="n">
-        <v>53676000</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>0→21</t>
-        </is>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>덕산네오룩스</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I38" s="15" t="n">
-        <v>-67984000</v>
-      </c>
-      <c r="J38" s="16" t="n">
-        <v>-0.191</v>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>42→14</t>
-        </is>
-      </c>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="8" t="n"/>
+      <c r="J38" s="8" t="n"/>
+      <c r="K38" s="8" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t>서진시스템</t>
-        </is>
-      </c>
-      <c r="B39" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>78736000</v>
-      </c>
-      <c r="D39" s="12" t="n">
-        <v>0.222</v>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>610→629</t>
-        </is>
-      </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>새로닉스</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
-        <v>-28</v>
-      </c>
-      <c r="I39" s="15" t="n">
-        <v>-23833600</v>
-      </c>
-      <c r="J39" s="16" t="n">
-        <v>-0.067</v>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>978→950</t>
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>더블유씨피</t>
         </is>
       </c>
       <c r="B40" s="11" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>53952000</v>
+        <v>63872000</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>0.152</v>
+        <v>0.175</v>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>43→55</t>
+          <t>2,940→3,020</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>LS증권</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>-13</v>
+        <v>-167</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-36504000</v>
+        <v>-90580800</v>
       </c>
       <c r="J40" s="16" t="n">
-        <v>-0.103</v>
+        <v>-0.247</v>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>40→27</t>
+          <t>452→285</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>성호전자</t>
+          <t>오로스테크놀로지</t>
         </is>
       </c>
       <c r="B41" s="11" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>19272000</v>
+        <v>41709600</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.054</v>
+        <v>0.114</v>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>77→88</t>
+          <t>58→85</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
-        <v>-13</v>
+        <v>-111</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-105040000</v>
+        <v>-221112000</v>
       </c>
       <c r="J41" s="16" t="n">
-        <v>-0.296</v>
+        <v>-0.604</v>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>98→85</t>
+          <t>647→536</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="B42" s="11" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>161040000</v>
+        <v>266200000</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.453</v>
+        <v>0.727</v>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>52→63</t>
+          <t>60→85</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>디아이티  (편출)</t>
+          <t>씨어스</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>-12</v>
+        <v>-110</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-17347200</v>
+        <v>-319000000</v>
       </c>
       <c r="J42" s="16" t="n">
-        <v>-0.049</v>
+        <v>-0.872</v>
       </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>12→0</t>
+          <t>843→733</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B43" s="11" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>110952000</v>
+        <v>93104000</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.312</v>
+        <v>0.254</v>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>39→48</t>
+          <t>134→157</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>다우데이타</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>-9</v>
+        <v>-32</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-61920000</v>
+        <v>-47820800</v>
       </c>
       <c r="J43" s="16" t="n">
-        <v>-0.174</v>
+        <v>-0.131</v>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>140→131</t>
+          <t>107→75</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>네패스아크  (신규)</t>
         </is>
       </c>
       <c r="B44" s="11" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>47152000</v>
+        <v>56868000</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.133</v>
+        <v>0.155</v>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>39→46</t>
+          <t>0→21</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>-9</v>
+        <v>-28</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-101304000</v>
+        <v>-23587200</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>-0.285</v>
+        <v>-0.064</v>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B45" s="11" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>99568000</v>
+        <v>77368000</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.28</v>
+        <v>0.211</v>
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>68→75</t>
+          <t>610→629</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>-5</v>
+        <v>-28</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-106200000</v>
+        <v>-72240000</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>-0.299</v>
+        <v>-0.197</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>32→27</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B46" s="11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>18320000</v>
+        <v>55392000</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.052</v>
+        <v>0.151</v>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>181→186</t>
+          <t>43→55</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>-4</v>
+        <v>-13</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-39904000</v>
+        <v>-111800000</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>-0.112</v>
+        <v>-0.305</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>77→73</t>
+          <t>98→85</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>성호전자</t>
         </is>
       </c>
       <c r="B47" s="11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>19460000</v>
+        <v>19448000</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>0.055</v>
+        <v>0.053</v>
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>77→88</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>코오롱티슈진</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>-3</v>
+        <v>-13</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-20904000</v>
+        <v>-36348000</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.059</v>
+        <v>-0.099</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>80→77</t>
+          <t>40→27</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>솔브레인</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>97120000</v>
+        <v>160424000</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>0.273</v>
+        <v>0.438</v>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>22→26</t>
-        </is>
-      </c>
-      <c r="G48" s="17" t="n"/>
-      <c r="H48" s="17" t="n"/>
-      <c r="I48" s="17" t="n"/>
-      <c r="J48" s="17" t="n"/>
-      <c r="K48" s="17" t="n"/>
+          <t>52→63</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>디아이티  (편출)</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I48" s="15" t="n">
+        <v>-18192000</v>
+      </c>
+      <c r="J48" s="16" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>12→0</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>티씨케이</t>
+          <t>ISC</t>
         </is>
       </c>
       <c r="B49" s="11" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>60240000</v>
+        <v>120240000</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>0.17</v>
+        <v>0.329</v>
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>44→47</t>
-        </is>
-      </c>
-      <c r="G49" s="17" t="n"/>
-      <c r="H49" s="17" t="n"/>
-      <c r="I49" s="17" t="n"/>
-      <c r="J49" s="17" t="n"/>
-      <c r="K49" s="17" t="n"/>
-    </row>
-    <row r="51" ht="19" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 8종목  /  매도 5종목</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
+          <t>39→48</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H49" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <v>-103608000</v>
+      </c>
+      <c r="J49" s="16" t="n">
+        <v>-0.283</v>
+      </c>
+      <c r="K49" s="13" t="inlineStr">
+        <is>
+          <t>116→107</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>씨엠티엑스</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>47208000</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>39→46</t>
+        </is>
+      </c>
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>비나텍</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <v>-60768000</v>
+      </c>
+      <c r="J50" s="16" t="n">
+        <v>-0.166</v>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>140→131</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>99288000</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>68→75</t>
+        </is>
+      </c>
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>파크시스템스</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I51" s="15" t="n">
+        <v>-104000000</v>
+      </c>
+      <c r="J51" s="16" t="n">
+        <v>-0.284</v>
+      </c>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>32→27</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="8" t="n"/>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>21640000</v>
+      </c>
+      <c r="D52" s="12" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>102→107</t>
+        </is>
+      </c>
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H52" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I52" s="15" t="n">
+        <v>-41312000</v>
+      </c>
+      <c r="J52" s="16" t="n">
+        <v>-0.113</v>
+      </c>
+      <c r="K52" s="13" t="inlineStr">
+        <is>
+          <t>77→73</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>전체대비비중</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>전체대비비중</t>
-        </is>
-      </c>
-      <c r="K53" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>인텍플러스</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>20720000</v>
+      </c>
+      <c r="D53" s="12" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>181→186</t>
+        </is>
+      </c>
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>코오롱티슈진</t>
+        </is>
+      </c>
+      <c r="H53" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I53" s="15" t="n">
+        <v>-21672000</v>
+      </c>
+      <c r="J53" s="16" t="n">
+        <v>-0.059</v>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>80→77</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="10" t="inlineStr">
         <is>
-          <t>큐리오시스  (신규)</t>
+          <t>솔브레인</t>
         </is>
       </c>
       <c r="B54" s="11" t="n">
-        <v>297</v>
+        <v>4</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>832312800</v>
+        <v>103200000</v>
       </c>
       <c r="D54" s="12" t="n">
-        <v>1.316</v>
+        <v>0.282</v>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>0→297</t>
-        </is>
-      </c>
-      <c r="G54" s="14" t="inlineStr">
-        <is>
-          <t>지아이이노베이션  (편출)</t>
-        </is>
-      </c>
-      <c r="H54" s="15" t="n">
-        <v>-685</v>
-      </c>
-      <c r="I54" s="15" t="n">
-        <v>-750828500</v>
-      </c>
-      <c r="J54" s="16" t="n">
-        <v>-1.187</v>
-      </c>
-      <c r="K54" s="13" t="inlineStr">
-        <is>
-          <t>685→0</t>
-        </is>
-      </c>
+          <t>22→26</t>
+        </is>
+      </c>
+      <c r="G54" s="17" t="n"/>
+      <c r="H54" s="17" t="n"/>
+      <c r="I54" s="17" t="n"/>
+      <c r="J54" s="17" t="n"/>
+      <c r="K54" s="17" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
+          <t>티씨케이</t>
         </is>
       </c>
       <c r="B55" s="11" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>146176800</v>
+        <v>58800000</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>0.231</v>
+        <v>0.161</v>
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>530→607</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>HLB이노베이션  (편출)</t>
-        </is>
-      </c>
-      <c r="H55" s="15" t="n">
-        <v>-622</v>
-      </c>
-      <c r="I55" s="15" t="n">
-        <v>-794934660</v>
-      </c>
-      <c r="J55" s="16" t="n">
-        <v>-1.257</v>
-      </c>
-      <c r="K55" s="13" t="inlineStr">
-        <is>
-          <t>622→0</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="10" t="inlineStr">
-        <is>
-          <t>디앤디파마텍</t>
-        </is>
-      </c>
-      <c r="B56" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C56" s="11" t="n">
-        <v>406212400</v>
-      </c>
-      <c r="D56" s="12" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>354→398</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>올릭스</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n">
-        <v>-122</v>
-      </c>
-      <c r="I56" s="15" t="n">
-        <v>-2058249800</v>
-      </c>
-      <c r="J56" s="16" t="n">
-        <v>-3.255</v>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>462→340</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="10" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="C57" s="11" t="n">
-        <v>726138000</v>
-      </c>
-      <c r="D57" s="12" t="n">
-        <v>1.148</v>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>152→187</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>리가켐바이오</t>
-        </is>
-      </c>
-      <c r="H57" s="15" t="n">
-        <v>-36</v>
-      </c>
-      <c r="I57" s="15" t="n">
-        <v>-543891600</v>
-      </c>
-      <c r="J57" s="16" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>395→359</t>
-        </is>
-      </c>
+          <t>44→47</t>
+        </is>
+      </c>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="17" t="n"/>
+      <c r="I55" s="17" t="n"/>
+      <c r="J55" s="17" t="n"/>
+      <c r="K55" s="17" t="n"/>
+    </row>
+    <row r="57" ht="19" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 632억      오늘 2026-07-06  vs  5일전 2026-06-29      매수 8종목  /  매도 5종목</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>펩트론</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="C58" s="11" t="n">
-        <v>653411200</v>
-      </c>
-      <c r="D58" s="12" t="n">
-        <v>1.033</v>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>30→62</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>알테오젠</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="n">
-        <v>-30</v>
-      </c>
-      <c r="I58" s="15" t="n">
-        <v>-1157685000</v>
-      </c>
-      <c r="J58" s="16" t="n">
-        <v>-1.831</v>
-      </c>
-      <c r="K58" s="13" t="inlineStr">
-        <is>
-          <t>174→144</t>
-        </is>
-      </c>
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n"/>
+      <c r="E58" s="6" t="n"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="8" t="n"/>
+      <c r="J58" s="8" t="n"/>
+      <c r="K58" s="8" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="10" t="inlineStr">
-        <is>
-          <t>한미약품</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="C59" s="11" t="n">
-        <v>1512335500</v>
-      </c>
-      <c r="D59" s="12" t="n">
-        <v>2.391</v>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>46→75</t>
-        </is>
-      </c>
-      <c r="G59" s="17" t="n"/>
-      <c r="H59" s="17" t="n"/>
-      <c r="I59" s="17" t="n"/>
-      <c r="J59" s="17" t="n"/>
-      <c r="K59" s="17" t="n"/>
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H59" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="inlineStr">
+        <is>
+          <t>전체대비비중</t>
+        </is>
+      </c>
+      <c r="K59" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>큐리오시스  (신규)</t>
         </is>
       </c>
       <c r="B60" s="11" t="n">
-        <v>14</v>
+        <v>297</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>539462000</v>
+        <v>854409600</v>
       </c>
       <c r="D60" s="12" t="n">
-        <v>0.853</v>
+        <v>1.352</v>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>32→46</t>
-        </is>
-      </c>
-      <c r="G60" s="17" t="n"/>
-      <c r="H60" s="17" t="n"/>
-      <c r="I60" s="17" t="n"/>
-      <c r="J60" s="17" t="n"/>
-      <c r="K60" s="17" t="n"/>
+          <t>0→297</t>
+        </is>
+      </c>
+      <c r="G60" s="14" t="inlineStr">
+        <is>
+          <t>지아이이노베이션  (편출)</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n">
+        <v>-685</v>
+      </c>
+      <c r="I60" s="15" t="n">
+        <v>-770762000</v>
+      </c>
+      <c r="J60" s="16" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>685→0</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
+          <t>리센스메디컬</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>150057600</v>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>0.237</v>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>530→607</t>
+        </is>
+      </c>
+      <c r="G61" s="14" t="inlineStr">
+        <is>
+          <t>HLB이노베이션  (편출)</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n">
+        <v>-622</v>
+      </c>
+      <c r="I61" s="15" t="n">
+        <v>-816039120</v>
+      </c>
+      <c r="J61" s="16" t="n">
+        <v>-1.291</v>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>622→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>디앤디파마텍</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>416996800</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>354→398</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n">
+        <v>-122</v>
+      </c>
+      <c r="I62" s="15" t="n">
+        <v>-2112893600</v>
+      </c>
+      <c r="J62" s="16" t="n">
+        <v>-3.343</v>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>462→340</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>745416000</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>1.179</v>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>152→187</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>리가켐바이오</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n">
+        <v>-36</v>
+      </c>
+      <c r="I63" s="15" t="n">
+        <v>-558331200</v>
+      </c>
+      <c r="J63" s="16" t="n">
+        <v>-0.883</v>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>395→359</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="10" t="inlineStr">
+        <is>
+          <t>펩트론</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>670758400</v>
+      </c>
+      <c r="D64" s="12" t="n">
+        <v>1.061</v>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>30→62</t>
+        </is>
+      </c>
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="I64" s="15" t="n">
+        <v>-1188420000</v>
+      </c>
+      <c r="J64" s="16" t="n">
+        <v>-1.88</v>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>174→144</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>한미약품</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>1552486000</v>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>46→75</t>
+        </is>
+      </c>
+      <c r="G65" s="17" t="n"/>
+      <c r="H65" s="17" t="n"/>
+      <c r="I65" s="17" t="n"/>
+      <c r="J65" s="17" t="n"/>
+      <c r="K65" s="17" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>553784000</v>
+      </c>
+      <c r="D66" s="12" t="n">
+        <v>0.876</v>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>32→46</t>
+        </is>
+      </c>
+      <c r="G66" s="17" t="n"/>
+      <c r="H66" s="17" t="n"/>
+      <c r="I66" s="17" t="n"/>
+      <c r="J66" s="17" t="n"/>
+      <c r="K66" s="17" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
           <t>에이비엘바이오</t>
         </is>
       </c>
-      <c r="B61" s="11" t="n">
+      <c r="B67" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C61" s="11" t="n">
-        <v>43437200</v>
-      </c>
-      <c r="D61" s="12" t="n">
-        <v>0.06900000000000001</v>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
+      <c r="C67" s="11" t="n">
+        <v>44590400</v>
+      </c>
+      <c r="D67" s="12" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>409→413</t>
         </is>
       </c>
-      <c r="G61" s="17" t="n"/>
-      <c r="H61" s="17" t="n"/>
-      <c r="I61" s="17" t="n"/>
-      <c r="J61" s="17" t="n"/>
-      <c r="K61" s="17" t="n"/>
-    </row>
-    <row r="63" ht="19" customHeight="1">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="G67" s="17" t="n"/>
+      <c r="H67" s="17" t="n"/>
+      <c r="I67" s="17" t="n"/>
+      <c r="J67" s="17" t="n"/>
+      <c r="K67" s="17" t="n"/>
+    </row>
+    <row r="69" ht="19" customHeight="1">
+      <c r="A69" s="18" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B63" s="19" t="n"/>
-      <c r="C63" s="19" t="n"/>
-      <c r="D63" s="19" t="n"/>
-      <c r="E63" s="19" t="n"/>
-      <c r="F63" s="19" t="n"/>
-      <c r="G63" s="19" t="n"/>
-      <c r="H63" s="19" t="n"/>
-      <c r="I63" s="19" t="n"/>
-      <c r="J63" s="19" t="n"/>
-      <c r="K63" s="19" t="n"/>
+      <c r="B69" s="19" t="n"/>
+      <c r="C69" s="19" t="n"/>
+      <c r="D69" s="19" t="n"/>
+      <c r="E69" s="19" t="n"/>
+      <c r="F69" s="19" t="n"/>
+      <c r="G69" s="19" t="n"/>
+      <c r="H69" s="19" t="n"/>
+      <c r="I69" s="19" t="n"/>
+      <c r="J69" s="19" t="n"/>
+      <c r="K69" s="19" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G52:K52"/>
+  <mergeCells count="21">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A69:K69"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="G28:K28"/>
+    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A27:K27"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A29:K29"/>
-    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="A57:K57"/>
+    <mergeCell ref="A33:E33"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A51:K51"/>
-    <mergeCell ref="A63:K63"/>
-    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="G58:K58"/>
+    <mergeCell ref="A32:K32"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A58:E58"/>
     <mergeCell ref="G22:K22"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20260706.xlsx
+++ b/reports/pdf_rolling5_20260706.xlsx
@@ -1019,21 +1019,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2166714000</v>
+        <v>472737600</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.402</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>33→39</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1059,21 +1059,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>472737600</v>
+        <v>2166714000</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.402</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>33→39</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260706.xlsx
+++ b/reports/pdf_rolling5_20260706.xlsx
@@ -1019,21 +1019,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>472737600</v>
+        <v>2166714000</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.402</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>33→39</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1059,21 +1059,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>2166714000</v>
+        <v>472737600</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.402</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>33→39</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1910,21 +1910,21 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-111800000</v>
+        <v>-36348000</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>-0.305</v>
+        <v>-0.099</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>98→85</t>
+          <t>40→27</t>
         </is>
       </c>
     </row>
@@ -1950,21 +1950,21 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-36348000</v>
+        <v>-111800000</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.099</v>
+        <v>-0.305</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>40→27</t>
+          <t>98→85</t>
         </is>
       </c>
     </row>
@@ -2030,82 +2030,82 @@
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H49" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-103608000</v>
+        <v>-60768000</v>
       </c>
       <c r="J49" s="16" t="n">
-        <v>-0.283</v>
+        <v>-0.166</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>116→107</t>
+          <t>140→131</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>47208000</v>
+        <v>99288000</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.129</v>
+        <v>0.271</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>39→46</t>
+          <t>68→75</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H50" s="15" t="n">
         <v>-9</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-60768000</v>
+        <v>-103608000</v>
       </c>
       <c r="J50" s="16" t="n">
-        <v>-0.166</v>
+        <v>-0.283</v>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>140→131</t>
+          <t>116→107</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>99288000</v>
+        <v>47208000</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.271</v>
+        <v>0.129</v>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>68→75</t>
+          <t>39→46</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2131,21 +2131,21 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>21640000</v>
+        <v>20720000</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>181→186</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2171,21 +2171,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>20720000</v>
+        <v>21640000</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>181→186</t>
+          <t>102→107</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20260706.xlsx
+++ b/reports/pdf_rolling5_20260706.xlsx
@@ -1019,21 +1019,21 @@
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>티엘비</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2166714000</v>
+        <v>472737600</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.402</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>33→39</t>
+          <t>174→180</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1059,21 +1059,21 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>티엘비</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>472737600</v>
+        <v>2166714000</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.402</v>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>174→180</t>
+          <t>33→39</t>
         </is>
       </c>
       <c r="G16" s="17" t="n"/>
@@ -1830,21 +1830,21 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>새로닉스</t>
+          <t>덕산네오룩스</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-23587200</v>
+        <v>-72240000</v>
       </c>
       <c r="J44" s="16" t="n">
-        <v>-0.064</v>
+        <v>-0.197</v>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>978→950</t>
+          <t>42→14</t>
         </is>
       </c>
     </row>
@@ -1870,21 +1870,21 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>덕산네오룩스</t>
+          <t>새로닉스</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-72240000</v>
+        <v>-23587200</v>
       </c>
       <c r="J45" s="16" t="n">
-        <v>-0.197</v>
+        <v>-0.064</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>42→14</t>
+          <t>978→950</t>
         </is>
       </c>
     </row>
@@ -1910,21 +1910,21 @@
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>삼현</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-36348000</v>
+        <v>-111800000</v>
       </c>
       <c r="J46" s="16" t="n">
-        <v>-0.099</v>
+        <v>-0.305</v>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>40→27</t>
+          <t>98→85</t>
         </is>
       </c>
     </row>
@@ -1950,21 +1950,21 @@
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>삼현</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
         <v>-13</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-111800000</v>
+        <v>-36348000</v>
       </c>
       <c r="J47" s="16" t="n">
-        <v>-0.305</v>
+        <v>-0.099</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>98→85</t>
+          <t>40→27</t>
         </is>
       </c>
     </row>
@@ -2051,21 +2051,21 @@
     <row r="50">
       <c r="A50" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B50" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>99288000</v>
+        <v>47208000</v>
       </c>
       <c r="D50" s="12" t="n">
-        <v>0.271</v>
+        <v>0.129</v>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>68→75</t>
+          <t>39→46</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -2091,21 +2091,21 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B51" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>47208000</v>
+        <v>99288000</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>0.129</v>
+        <v>0.271</v>
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>39→46</t>
+          <t>68→75</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -2131,21 +2131,21 @@
     <row r="52">
       <c r="A52" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="B52" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>20720000</v>
+        <v>21640000</v>
       </c>
       <c r="D52" s="12" t="n">
-        <v>0.057</v>
+        <v>0.059</v>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>181→186</t>
+          <t>102→107</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -2171,21 +2171,21 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B53" s="11" t="n">
         <v>5</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>21640000</v>
+        <v>20720000</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>0.059</v>
+        <v>0.057</v>
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>102→107</t>
+          <t>181→186</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
